--- a/nriss-patch-2/ig/StructureDefinition-fr-encounter-care-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-encounter-care-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -631,7 +631,7 @@
     <t>estimatedDischargeDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-estimated-discharge-date|2.2.0}
 </t>
   </si>
   <si>
@@ -741,7 +741,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-identifier-type|2.2.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -827,7 +827,7 @@
     <t>Encounter.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1123,7 +1123,7 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-type|2.2.0</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1181,7 +1181,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1324,7 +1324,7 @@
     <t>Encounter.participant.individual</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.1.0|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1419,7 +1419,7 @@
     <t>Encounter.appointment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-appointment|2.2.0)
 </t>
   </si>
   <si>
@@ -1697,7 +1697,7 @@
     <t>Encounter.hospitalization.origin</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1842,7 +1842,7 @@
     <t>Category or kind of location after discharge.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-encounter-discharge-disposition|2.2.0</t>
   </si>
   <si>
     <t>.dischargeDispositionCode</t>
@@ -1931,7 +1931,7 @@
 There may be many levels in the hierachy, and this may only pic specific levels that are required for a specific usage scenario.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-physical-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-location-type|2.2.0</t>
   </si>
   <si>
     <t>Encounter.location.period</t>
@@ -1961,7 +1961,7 @@
     <t>Encounter.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
